--- a/MinMax/scripts/comparison/accuracy_comparison_table_118_5_False.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_118_5_False.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Pg Vm Projection False</t>
   </si>
@@ -31,88 +31,91 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>sample_num</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
     <t>pinj_tot</t>
   </si>
   <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>Iinj_i_tot</t>
+  </si>
+  <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
     <t>pd_tot</t>
   </si>
   <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>solve_time</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
     <t>slack_tot</t>
   </si>
   <si>
-    <t>solve_time</t>
+    <t>qg_tot</t>
   </si>
   <si>
     <t>vm_tot</t>
   </si>
   <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
     <t>Ibr_from_r_tot</t>
   </si>
   <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>Iinj_i_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>2.33 (1.34)</t>
-  </si>
-  <si>
-    <t>2.19s (5.96 s)</t>
-  </si>
-  <si>
-    <t>87316.92 (67523.48 &gt; 29.48%)</t>
-  </si>
-  <si>
-    <t>1.21 (1.34)</t>
-  </si>
-  <si>
-    <t>0.81s (5.96 s)</t>
-  </si>
-  <si>
-    <t>70416.06 (67523.48 &gt; 4.15%)</t>
-  </si>
-  <si>
-    <t>1.33 (1.34)</t>
-  </si>
-  <si>
-    <t>5.37s (5.96 s)</t>
-  </si>
-  <si>
-    <t>67519.80 (67523.48 &gt; 0.01%)</t>
-  </si>
-  <si>
-    <t>2.82s (5.96 s)</t>
+    <t>0.22s (0.18 s)</t>
+  </si>
+  <si>
+    <t>87338.83 (67523.48 &gt; 29.35%)</t>
+  </si>
+  <si>
+    <t>233.05 (133.88)</t>
+  </si>
+  <si>
+    <t>0.21s (0.18 s)</t>
+  </si>
+  <si>
+    <t>70357.01 (67523.48 &gt; 4.20%)</t>
+  </si>
+  <si>
+    <t>120.73 (133.88)</t>
+  </si>
+  <si>
+    <t>0.17s (0.18 s)</t>
+  </si>
+  <si>
+    <t>67523.34 (67523.48 &gt; 0.00%)</t>
+  </si>
+  <si>
+    <t>133.89 (133.88)</t>
+  </si>
+  <si>
+    <t>0.19s (0.18 s)</t>
   </si>
 </sst>
 </file>
@@ -470,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -494,68 +497,56 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>0.4248986542224884</v>
-      </c>
-      <c r="C2">
-        <v>0.01457957457751036</v>
-      </c>
-      <c r="D2">
-        <v>3.551632289600093E-06</v>
-      </c>
-      <c r="E2">
-        <v>3.551632289600093E-06</v>
-      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3">
-        <v>1.914293666701331E-16</v>
+        <v>0.0006229935679584742</v>
       </c>
       <c r="C3">
-        <v>1.914293666701331E-16</v>
+        <v>0.0005704739596694708</v>
       </c>
       <c r="D3">
-        <v>1.914293666701331E-16</v>
+        <v>9.467426571063697E-05</v>
       </c>
       <c r="E3">
-        <v>1.914293666701331E-16</v>
+        <v>0.000250914366915822</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
+      <c r="B4">
+        <v>0.4420393109321594</v>
+      </c>
+      <c r="C4">
+        <v>0.03179654851555824</v>
+      </c>
+      <c r="D4">
+        <v>0.003132597776129842</v>
+      </c>
+      <c r="E4">
+        <v>0.007848183624446392</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
+      <c r="B5">
+        <v>0.0866280198097229</v>
+      </c>
+      <c r="C5">
+        <v>0.0864085853099823</v>
+      </c>
+      <c r="D5">
+        <v>0.08614829927682877</v>
+      </c>
+      <c r="E5">
+        <v>0.08615070581436157</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -563,16 +554,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>8.319743938045576E-05</v>
+        <v>0.3625271022319794</v>
       </c>
       <c r="C6">
-        <v>2.059482176264282E-05</v>
+        <v>0.02938017062842846</v>
       </c>
       <c r="D6">
-        <v>1.105430055758916E-05</v>
+        <v>0.002892863936722279</v>
       </c>
       <c r="E6">
-        <v>1.105430055758916E-05</v>
+        <v>0.007075903937220573</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -580,16 +571,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>0.9252447485923767</v>
+        <v>0.0005066405865363777</v>
       </c>
       <c r="C7">
-        <v>0.03178891539573669</v>
+        <v>5.824375330121256E-05</v>
       </c>
       <c r="D7">
-        <v>6.847178156021982E-06</v>
+        <v>4.424558937898837E-06</v>
       </c>
       <c r="E7">
-        <v>6.847178156021982E-06</v>
+        <v>1.118042473535752E-05</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -597,33 +588,33 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.02038352750241756</v>
+        <v>0.07015083730220795</v>
       </c>
       <c r="C8">
-        <v>0.000115565890155267</v>
+        <v>0.01292383205145597</v>
       </c>
       <c r="D8">
-        <v>1.450050262974401E-06</v>
+        <v>0.0003065687487833202</v>
       </c>
       <c r="E8">
-        <v>1.450050262974401E-06</v>
+        <v>0.0009806499583646655</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
+      <c r="B9">
+        <v>0.9512978792190552</v>
+      </c>
+      <c r="C9">
+        <v>0.0489463210105896</v>
+      </c>
+      <c r="D9">
+        <v>0.004019788466393948</v>
+      </c>
+      <c r="E9">
+        <v>0.009233118034899235</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -631,16 +622,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>2.491211909892073E-17</v>
+        <v>0.00379946967586875</v>
       </c>
       <c r="C10">
-        <v>2.491211909892073E-17</v>
+        <v>0.004054593853652477</v>
       </c>
       <c r="D10">
-        <v>2.491211909892073E-17</v>
+        <v>0.0007180292159318924</v>
       </c>
       <c r="E10">
-        <v>2.491211909892073E-17</v>
+        <v>0.001902028103359044</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -648,16 +639,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>0.0418841615319252</v>
+        <v>0.5232820510864258</v>
       </c>
       <c r="C11">
-        <v>0.03406977653503418</v>
+        <v>0.5182748436927795</v>
       </c>
       <c r="D11">
-        <v>0.007935475558042526</v>
+        <v>0.5177391767501831</v>
       </c>
       <c r="E11">
-        <v>0.007935476489365101</v>
+        <v>0.5177801847457886</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -665,33 +656,33 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.0001286963524762541</v>
+        <v>0.1010593846440315</v>
       </c>
       <c r="C12">
-        <v>1.833808892115485E-05</v>
+        <v>0.1006878614425659</v>
       </c>
       <c r="D12">
-        <v>1.049709590006387E-05</v>
+        <v>0.1004736796021461</v>
       </c>
       <c r="E12">
-        <v>1.049709590006387E-05</v>
+        <v>0.1004760190844536</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13">
-        <v>0.2903816401958466</v>
-      </c>
-      <c r="C13">
-        <v>0.005725611466914415</v>
-      </c>
-      <c r="D13">
-        <v>1.754735058057122E-05</v>
-      </c>
-      <c r="E13">
-        <v>1.754735058057122E-05</v>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -699,33 +690,33 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.01940900273621082</v>
+        <v>0.0209803469479084</v>
       </c>
       <c r="C14">
-        <v>0.007310844026505947</v>
+        <v>0.001496960292570293</v>
       </c>
       <c r="D14">
-        <v>0.001348192454315722</v>
+        <v>0.0001422558852937073</v>
       </c>
       <c r="E14">
-        <v>0.001348192454315722</v>
+        <v>0.0004567840369418263</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15">
-        <v>0.2759514153003693</v>
-      </c>
-      <c r="C15">
-        <v>0.005525896325707436</v>
-      </c>
-      <c r="D15">
-        <v>1.745270128594711E-05</v>
-      </c>
-      <c r="E15">
-        <v>1.745270128594711E-05</v>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -733,33 +724,33 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.06967280805110931</v>
+        <v>0.02096208930015564</v>
       </c>
       <c r="C16">
-        <v>0.01758915185928345</v>
+        <v>0.01261635590344667</v>
       </c>
       <c r="D16">
-        <v>0.006221320480108261</v>
+        <v>0.000231012498261407</v>
       </c>
       <c r="E16">
-        <v>0.006221320480108261</v>
+        <v>0.0008113113581202924</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B17">
-        <v>0.01920445822179317</v>
-      </c>
-      <c r="C17">
-        <v>0.00717949727550149</v>
-      </c>
-      <c r="D17">
-        <v>0.001343585783615708</v>
-      </c>
-      <c r="E17">
-        <v>0.001343585783615708</v>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -767,16 +758,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>0.02211357839405537</v>
+        <v>0.03966474160552025</v>
       </c>
       <c r="C18">
-        <v>0.01844529062509537</v>
+        <v>0.02846540883183479</v>
       </c>
       <c r="D18">
-        <v>0.006805455312132835</v>
+        <v>0.0007159910164773464</v>
       </c>
       <c r="E18">
-        <v>0.006805455312132835</v>
+        <v>0.002175634726881981</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -784,16 +775,33 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>0.3495281636714935</v>
+        <v>0.0006658268976025283</v>
       </c>
       <c r="C19">
-        <v>0.01328859478235245</v>
+        <v>2.378572207817342E-05</v>
       </c>
       <c r="D19">
-        <v>6.426431355066597E-05</v>
+        <v>1.023774871100613E-06</v>
       </c>
       <c r="E19">
-        <v>6.426431355066597E-05</v>
+        <v>2.197095000155969E-06</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.5449681282043457</v>
+      </c>
+      <c r="C20">
+        <v>0.5396432876586914</v>
+      </c>
+      <c r="D20">
+        <v>0.539089560508728</v>
+      </c>
+      <c r="E20">
+        <v>0.5391308665275574</v>
       </c>
     </row>
   </sheetData>
